--- a/uat-test-plans-reduced30/G2-16396-wishlist-multiple-wl.xlsx
+++ b/uat-test-plans-reduced30/G2-16396-wishlist-multiple-wl.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~25% — 12/16 checks retained, lowest-priority sections dropped] 15 UI-testable child stories mapped to 16 detailed business checklist checks; 16 non-UI/technical or spike stories excluded from business execution scope.</t>
+          <t>[Reduced V2 ~25% — 12/16 checks retained; AC and core-case coverage guardrails enforced] 15 UI-testable child stories mapped to 16 detailed business checklist checks; 16 non-UI/technical or spike stories excluded from business execution scope.</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=18835; payload_chars=18829; est_tokens~4708; checklist_rows=12; matrix_rows=15; exploratory_rows=4</t>
+          <t>payload_bytes=17800; payload_chars=17794; est_tokens~4449; checklist_rows=12; matrix_rows=12; exploratory_rows=4</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
     <row r="5" ht="49" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-005</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -899,32 +899,33 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Wishlist Navigation</t>
+          <t>PDP &amp; MiniPDP Add-to-Wishlist</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Use wishlist navigation controls/icons to switch or manage lists</t>
+          <t>Add item to wishlist from PDP or MiniPDP when user has multiple lists</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Verify create/edit/remove controls are visible in expected contexts and switch between all-items and single-list views.</t>
+          <t>1. On PDP and MiniPDP, open add-to-wishlist control and choose a specific wishlist.
+2. Then verify item appears in chosen list.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Controls are visible in the correct context.
-Navigation updates content for the selected view.</t>
+          <t>Control exposes wishlist choice when multiple lists exist.
+Item is added to the intended wishlist.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
     </row>
-    <row r="6" ht="49" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-008</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -934,33 +935,32 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>PDP &amp; MiniPDP Add-to-Wishlist</t>
+          <t>Single-WL Redirect</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Add item to wishlist from PDP or MiniPDP when user has multiple lists</t>
+          <t>Validate redirect behavior for users with exactly one wishlist</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1. On PDP and MiniPDP, open add-to-wishlist control and choose a specific wishlist.
-2. Then verify item appears in chosen list.</t>
+          <t>Login with a single-wishlist account and enter wishlist via navigation entry point.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Control exposes wishlist choice when multiple lists exist.
-Item is added to the intended wishlist.</t>
+          <t>User lands directly on the only wishlist.
+No unnecessary list selector step is shown.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
     </row>
-    <row r="7" ht="49" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-009</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -970,23 +970,23 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>All Items Query &amp; Rendering</t>
+          <t>Delete Item Across Lists</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Validate all-items view and per-list filtering behavior</t>
+          <t>Delete an item from multiple wishlists context and verify effect</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Open wishlist all-items view, then filter to specific lists and compare item counts/list membership.</t>
+          <t>From all-items view, delete a product associated with multiple wishlists and review list states.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>All-items view renders combined entries.
-Filtering isolates expected list items without stale data.</t>
+          <t>Deletion applies to the intended multi-list context.
+Removed item no longer appears where expected.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -995,7 +995,7 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UAT-007</t>
+          <t>UAT-010</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1005,33 +1005,33 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Auth Continuity</t>
+          <t>Undo Item Removal &amp; Error Handling</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Ensure login flow preserves multi-wishlist intent</t>
+          <t>Undo a multi-wishlist item removal and validate modal/API error handling</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1. While logged out, attempt a wishlist action that requires auth
-2. complete login and verify intended wishlist action can be completed.</t>
+          <t>1. Trigger item deletion and immediate undo
+2. also force/observe backend error path for create/rename on MRP to validate user message.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>After login, user is returned to a valid wishlist context.
-Action can be completed without losing intent.</t>
+          <t>Undo restores the item associations correctly.
+Error message is clear and user can recover/retry.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>UAT-008</t>
+          <t>UAT-012</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1041,23 +1041,24 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Single-WL Redirect</t>
+          <t>Modal Validation</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Validate redirect behavior for users with exactly one wishlist</t>
+          <t>Create/Rename modal validates duplicate name behavior and displays clear error state</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Login with a single-wishlist account and enter wishlist via navigation entry point.</t>
+          <t>1. Attempt to create or rename a wishlist using a name that already exists.
+2. Observe inline validation text, field styling, and retry behavior.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>User lands directly on the only wishlist.
-No unnecessary list selector step is shown.</t>
+          <t>Duplicate name attempt is blocked with clear inline error text.
+User can correct input and submit successfully without refreshing.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -1066,7 +1067,7 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>UAT-009</t>
+          <t>UAT-013</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1076,23 +1077,24 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Delete Item Across Lists</t>
+          <t>Modal Cancel Safety</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Delete an item from multiple wishlists context and verify effect</t>
+          <t>Cancel or close actions in create/rename/remove modals do not mutate data</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>From all-items view, delete a product associated with multiple wishlists and review list states.</t>
+          <t>1. Open create/rename/remove modal flows and dismiss via Cancel and close icon.
+2. Re-open list state and verify no rename, create, or remove was applied.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Deletion applies to the intended multi-list context.
-Removed item no longer appears where expected.</t>
+          <t>Dismissing modal performs no mutation.
+List names and membership remain unchanged after cancel/close.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -1101,7 +1103,7 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>UAT-010</t>
+          <t>UAT-014</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1111,24 +1113,24 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Undo Item Removal &amp; Error Handling</t>
+          <t>Post-Remove Stability</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Undo a multi-wishlist item removal and validate modal/API error handling</t>
+          <t>After removing a custom wishlist, user lands in a stable fallback view</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1. Trigger item deletion and immediate undo
-2. also force/observe backend error path for create/rename on MRP to validate user message.</t>
+          <t>1. Remove a custom wishlist while viewing it.
+2. Verify landing context (remaining list/all-items), selected navigation state, and absence of broken links.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Undo restores the item associations correctly.
-Error message is clear and user can recover/retry.</t>
+          <t>User is redirected to a valid remaining context after removal.
+No broken or stale selected-list state remains.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -1137,7 +1139,7 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>UAT-011</t>
+          <t>UAT-015</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1147,24 +1149,23 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Default Wishlist Guardrails</t>
+          <t>MiniPDP Targeting</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Default wishlist cannot be renamed or removed</t>
+          <t>MiniPDP wishlist dropdown adds product to the explicitly selected list</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1. Open the default wishlist and inspect available actions in wishlist navigation/edit controls.
-2. Compare against a custom wishlist.</t>
+          <t>From MiniPDP with multiple wishlists, choose a non-default target list, add item, then navigate to that list and at least one other list.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Default wishlist does not expose Rename/Remove actions.
-Custom wishlists expose Rename/Remove in expected contexts.</t>
+          <t>Item appears in selected target wishlist.
+Item does not appear in unrelated list unless previously saved there.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -1173,7 +1174,7 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>UAT-012</t>
+          <t>UAT-016</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1183,24 +1184,23 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Modal Validation</t>
+          <t>All Items Consistency</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Create/Rename modal validates duplicate name behavior and displays clear error state</t>
+          <t>All-items counts and membership stay consistent after delete and undo across multiple lists</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>1. Attempt to create or rename a wishlist using a name that already exists.
-2. Observe inline validation text, field styling, and retry behavior.</t>
+          <t>Save one product into multiple wishlists, delete it from All Items, confirm counters/membership updates, then undo and verify full restoration.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Duplicate name attempt is blocked with clear inline error text.
-User can correct input and submit successfully without refreshing.</t>
+          <t>Delete updates list membership and counters consistently.
+Undo restores previous membership/counter state without duplicates.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1225,7 +1225,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-002, UAT-012</t>
+          <t>UAT-001, UAT-002, UAT-012, UAT-013</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-016</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-003</t>
+          <t>UAT-003, UAT-013, UAT-014</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="7" ht="49" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>COV-006</t>
+          <t>COV-007</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>G2-19105</t>
+          <t>G2-19106</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Create/edit/remove nav icon affordances are present in wishlist navigation</t>
+          <t>Rename/add modal behavior and visual interaction remain consistent</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1583,97 +1583,97 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>UAT-004, UAT-011</t>
+          <t>UAT-002</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>PR #559 [G2-19105] Add create and edit icons to wishlist nav menu (mytheresa/atelier, closed).</t>
+          <t>No PR hit found in mytheresa/atelier for Jira key G2-19106; fallback Jira metadata used.</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Story has limited structured AC text; validation relies on summary/context and linked behavior tickets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>COV-008</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>G2-19107</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Remove modal presents clear confirm/cancel behavior for custom lists</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>UAT-003, UAT-013</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>PR #569 [G2-19107] Remove wishlist modal (mytheresa/atelier, closed).</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>COV-007</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>G2-19106</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Rename/add modal behavior and visual interaction remain consistent</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>UAT-002</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>No PR hit found in mytheresa/atelier for Jira key G2-19106; fallback Jira metadata used.</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Unavailable</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Story has limited structured AC text; validation relies on summary/context and linked behavior tickets.</t>
-        </is>
-      </c>
+      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>COV-008</t>
+          <t>COV-010</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>G2-19107</t>
+          <t>G2-21293</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Remove modal presents clear confirm/cancel behavior for custom lists</t>
+          <t>MiniPDP wishlist control becomes dropdown when user has &gt;1 wishlist</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>UAT-003</t>
+          <t>UAT-005, UAT-015</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>PR #569 [G2-19107] Remove wishlist modal (mytheresa/atelier, closed).</t>
+          <t>PR #596 [G2-21293] Add wishlist selector dropdown on mini PDP (mytheresa/atelier, closed).</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1713,20 +1713,20 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr"/>
     </row>
-    <row r="10" ht="49" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>COV-009</t>
+          <t>COV-012</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>G2-20842</t>
+          <t>G2-22969</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1736,17 +1736,17 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Auth/login flow supports multi-wishlist add flow continuity</t>
+          <t>Delete product action works from multiple-wishlist context</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>UAT-007</t>
+          <t>UAT-009, UAT-016</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>No PR hit found in mytheresa/atelier for Jira key G2-20842; fallback Jira metadata used.</t>
+          <t>PR #825 [G2-22969] Delete product from multiple wishlists (mytheresa/atelier, closed).</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1769,21 +1769,17 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Story has limited structured AC text; validation relies on summary/context and linked behavior tickets.</t>
-        </is>
-      </c>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>COV-010</t>
+          <t>COV-013</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>G2-21293</t>
+          <t>G2-23030</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>MiniPDP wishlist control becomes dropdown when user has &gt;1 wishlist</t>
+          <t>Undo restores product after multi-wishlist deletion</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1803,7 +1799,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-010, UAT-016</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1813,7 +1809,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>PR #596 [G2-21293] Add wishlist selector dropdown on mini PDP (mytheresa/atelier, closed).</t>
+          <t>PR #845 [G2-23030] Undo product from multiple wishlists (mytheresa/atelier, closed).</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1831,12 +1827,12 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>COV-011</t>
+          <t>COV-014</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>G2-22343</t>
+          <t>G2-23523</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1846,252 +1842,93 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Wishlist title truncation and responsive collapse on bp1/bp2</t>
+          <t>Single-wishlist users are redirected directly to their only wishlist</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>PR #778 [G2-23523] Default wishlist redirect (mytheresa/atelier, closed).</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="49" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>COV-015</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>G2-23730</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Create/rename modal displays BE error message correctly on MRP</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>UAT-004</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>PR #598 [G2-22343] Wishlist navigation improvements (mytheresa/atelier, closed).</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010, UAT-012</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>PR #776 [G2-23730] Duplicated default wishlist name error text (mytheresa/atelier, closed).</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>COV-012</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>G2-22969</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Delete product action works from multiple-wishlist context</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>UAT-009</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>PR #825 [G2-22969] Delete product from multiple wishlists (mytheresa/atelier, closed).</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>COV-013</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>G2-23030</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Undo restores product after multi-wishlist deletion</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>UAT-010</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>PR #845 [G2-23030] Undo product from multiple wishlists (mytheresa/atelier, closed).</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>COV-014</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>G2-23523</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Single-wishlist users are redirected directly to their only wishlist</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>UAT-008</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>PR #778 [G2-23523] Default wishlist redirect (mytheresa/atelier, closed).</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="49" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>COV-015</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>G2-23730</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Create/rename modal displays BE error message correctly on MRP</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>UAT-010, UAT-012</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>PR #776 [G2-23730] Duplicated default wishlist name error text (mytheresa/atelier, closed).</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Resilience</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uat-test-plans-reduced30/G2-16396-wishlist-multiple-wl.xlsx
+++ b/uat-test-plans-reduced30/G2-16396-wishlist-multiple-wl.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~25% — 12/16 checks retained; AC and core-case coverage guardrails enforced] 15 UI-testable child stories mapped to 16 detailed business checklist checks; 16 non-UI/technical or spike stories excluded from business execution scope.</t>
+          <t>[Reduced V2 ~25% — 12/16 checks retained; AC coverage guardrail enforced] 15 UI-testable child stories mapped to 16 detailed business checklist checks; 16 non-UI/technical or spike stories excluded from business execution scope.</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=17800; payload_chars=17794; est_tokens~4449; checklist_rows=12; matrix_rows=12; exploratory_rows=4</t>
+          <t>payload_bytes=17785; payload_chars=17779; est_tokens~4445; checklist_rows=12; matrix_rows=12; exploratory_rows=4</t>
         </is>
       </c>
     </row>
